--- a/output/pdf_financials_xlsx/MSC.xlsx
+++ b/output/pdf_financials_xlsx/MSC.xlsx
@@ -6149,16 +6149,16 @@
         <v>0.721602</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.721602</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.722753</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.036361</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.060366</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -7619,49 +7619,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.034997</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.013495</v>
+        <v>-2.882098</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.165856</v>
+        <v>-0.43407</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.015</v>
+        <v>-0.231377</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>2.134004</v>
+        <v>1.987037</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.078276</v>
+        <v>-0.132486</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.052653</v>
+        <v>-0.360252</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.074318</v>
+        <v>-0.248808</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.050328</v>
+        <v>-0.083389</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.021532</v>
+        <v>-0.127852</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.0166</v>
+        <v>-0.077096</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.085703</v>
+        <v>-0.015347</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>6.553445</v>
+        <v>6.48661</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.072479</v>
+        <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.115374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -13935,7 +13935,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -26663,7 +26667,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -30462,7 +30470,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -36022,7 +36034,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MSC.xlsx
+++ b/output/pdf_financials_xlsx/MSC.xlsx
@@ -931,37 +931,37 @@
         <v>0.08317099999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.097149</v>
+        <v>2.312892</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.06400699999999999</v>
+        <v>0.321407</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.179891</v>
+        <v>0.242951</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.16059</v>
+        <v>0.600305</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.154744</v>
+        <v>0.300805</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.219996</v>
+        <v>0.352666</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.089437</v>
+        <v>0.30898</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.057928</v>
+        <v>0.192544</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.032152</v>
+        <v>6.639736</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.024889</v>
+        <v>0.166695</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.03757</v>
+        <v>0.207539</v>
       </c>
     </row>
     <row r="11">
@@ -992,25 +992,25 @@
         <v>-0.196888</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.06400699999999999</v>
+        <v>-0.321407</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.179891</v>
+        <v>-0.242951</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.16059</v>
+        <v>-0.600305</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.154744</v>
+        <v>-0.300805</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.219996</v>
+        <v>-0.352666</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.089437</v>
+        <v>-0.30898</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.057928</v>
+        <v>-0.192544</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>-6.639736</v>
@@ -2444,49 +2444,49 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.201661</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.165476</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.102038</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000335</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002924</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.031318</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.077367</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.305321</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.015347</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004368</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.013277</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.003431</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001565</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.043426</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.035773</v>
       </c>
     </row>
     <row r="35">
@@ -2568,49 +2568,49 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.201661</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.165476</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.102038</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000335</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002924</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.031318</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.077367</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.305321</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.015347</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004368</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.013277</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.003431</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001565</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.043426</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.035773</v>
       </c>
     </row>
     <row r="37">
@@ -3312,43 +3312,43 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.217903</v>
+        <v>0.016242</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.206543</v>
+        <v>0.041067</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.12089</v>
+        <v>0.018852</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.002976</v>
+        <v>0.002641</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002924</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.031318</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.116984</v>
+        <v>0.039617</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.33125</v>
+        <v>0.025929</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.06259000000000001</v>
+        <v>0.047243</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.004368</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.017205</v>
+        <v>0.003928</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.003556</v>
+        <v>0.000125</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.00169</v>
+        <v>0.000125</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -38414,7 +38414,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -38693,7 +38693,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -40532,7 +40532,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">

--- a/output/pdf_financials_xlsx/MSC.xlsx
+++ b/output/pdf_financials_xlsx/MSC.xlsx
@@ -739,55 +739,55 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.051813</v>
+        <v>0.083563</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.044718</v>
+        <v>0.07571799999999999</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.051127</v>
+        <v>0.08212700000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.068954</v>
+        <v>0.099954</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.057991</v>
+        <v>0.093741</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.034978</v>
+        <v>0.07403899999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.013714</v>
+        <v>0.044214</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.017319</v>
+        <v>0.049069</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.159428</v>
+        <v>0.191678</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.139574</v>
+        <v>0.173074</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.127708</v>
+        <v>0.161458</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.177517</v>
+        <v>0.210267</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.089437</v>
+        <v>0.114937</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.057928</v>
+        <v>0.078553</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.032152</v>
+        <v>0.053652</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.024889</v>
+        <v>0.051639</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.03757</v>
+        <v>0.06482</v>
       </c>
     </row>
     <row r="8">
@@ -913,22 +913,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.12263</v>
+        <v>0.15438</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.08097699999999999</v>
+        <v>0.111977</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.088894</v>
+        <v>0.119894</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.162273</v>
+        <v>0.193273</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.123517</v>
+        <v>0.159267</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.08317099999999999</v>
+        <v>0.122232</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>2.312892</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.12263</v>
+        <v>-0.15438</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.08097699999999999</v>
+        <v>-0.111977</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.398663</v>
@@ -1264,7 +1264,7 @@
         <v>-4.340645</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.903325</v>
+        <v>-0.8820750000000001</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.893456</v>
@@ -1322,7 +1322,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.02125</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -2014,7 +2014,7 @@
         <v>-4.340645</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.903325</v>
+        <v>-0.8820750000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.893456</v>
@@ -2130,7 +2130,7 @@
         <v>-4.339618</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.902301</v>
+        <v>-0.881051</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.89191</v>
@@ -2280,7 +2280,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.409092197375507</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -6633,16 +6633,16 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013411</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020156</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.021171</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.016211</v>
       </c>
       <c r="H101" s="3" t="n">
         <v>0.00077</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.007227</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -28472,7 +28472,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -29775,7 +29779,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -33456,7 +33464,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -35442,7 +35454,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -36648,7 +36664,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -37949,7 +37969,11 @@
           <t>Directors' fees (Note 8)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -40241,7 +40265,11 @@
           <t>Directors' fees (Note 9)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -42510,7 +42538,11 @@
           <t>Directors' fees (Note 10)</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -49086,7 +49118,11 @@
           <t>Director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -53135,7 +53171,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -58636,7 +58676,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E505" s="5" t="n">
         <v>0.03175</v>
       </c>
@@ -59333,7 +59377,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
